--- a/data/source/ArtLoka_Product_Catalog_Full_ALK006-032.xlsx
+++ b/data/source/ArtLoka_Product_Catalog_Full_ALK006-032.xlsx
@@ -28,21 +28,14 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -57,12 +50,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -428,33 +418,34 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X9"/>
+  <dimension ref="A1:Y17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
-    <col width="34" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="30" customWidth="1" min="16" max="16"/>
-    <col width="22" customWidth="1" min="17" max="17"/>
-    <col width="26" customWidth="1" min="18" max="18"/>
-    <col width="34" customWidth="1" min="19" max="19"/>
-    <col width="36" customWidth="1" min="20" max="20"/>
-    <col width="40" customWidth="1" min="21" max="21"/>
-    <col width="40" customWidth="1" min="22" max="22"/>
-    <col width="26" customWidth="1" min="23" max="23"/>
-    <col width="50" customWidth="1" min="24" max="24"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="42" customWidth="1" min="13" max="13"/>
+    <col width="42" customWidth="1" min="14" max="14"/>
+    <col width="42" customWidth="1" min="15" max="15"/>
+    <col width="42" customWidth="1" min="16" max="16"/>
+    <col width="40" customWidth="1" min="17" max="17"/>
+    <col width="42" customWidth="1" min="18" max="18"/>
+    <col width="42" customWidth="1" min="19" max="19"/>
+    <col width="42" customWidth="1" min="20" max="20"/>
+    <col width="42" customWidth="1" min="21" max="21"/>
+    <col width="42" customWidth="1" min="22" max="22"/>
+    <col width="40" customWidth="1" min="23" max="23"/>
+    <col width="42" customWidth="1" min="24" max="24"/>
+    <col width="25" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -578,6 +569,11 @@
           <t>QA Notes / Flags</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Listing Status</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -585,8 +581,10 @@
           <t>ALK-018</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>2</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -605,7 +603,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>A dual-rod brass frame supports a beautifully illuminated globe shade in this mid-century-styled sconce, casting soft, ambient light both up and down the wall for a warm, layered glow. Its minimalist silhouette and round metal accents suit both residential and boutique-style interiors, from living room accent walls to hallway runs. Custom sizing is available on request, and every fixture is finished by hand.</t>
+          <t>ArtLoka's Mid-Century Globe Wall Sconce pairs a dual-rod brass frame with a luminous glass globe shade, casting soft ambient light up and down any wall.Two slender brass rods reach out from the wall like a sculptor's brushstroke, cradling a round shade that seems to hover rather than hang. Switch it on and the light spreads both upward and downward in a soft, layered wash instead of one harsh beam — the kind of glow that turns a reading corner into a retreat and a living room into something closer to a gallery.The silhouette borrows freely from mid-century design language: clean lines, a dual-rod frame, and a single circular accent that plays with symmetry instead of clutter. It's substantial enough to anchor a bare wall as its own statement, yet restrained enough to sit beside a sofa, a headboard, or a hallway console without crowding the space.Every fixture is hand-assembled and hand-finished by ArtLoka's artisans in India, so the brass carries the same warmth and small, honest imperfections that separate handmade lighting from anything mass-produced. Pair it with a warm white bulb for an intimate, amber-lit evening glow, or a cooler LED for a crisper, gallery-like wash.It's an easy fixture to specify in pairs, flanking a sofa or a bed, for a room that feels balanced and intentional rather than accidental.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -623,14 +621,20 @@
           <t>Metal frame, glass shade</t>
         </is>
       </c>
-      <c r="J2" t="n">
-        <v>10</v>
-      </c>
-      <c r="K2" t="n">
-        <v>25</v>
-      </c>
-      <c r="L2" t="n">
-        <v>10</v>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -684,12 +688,17 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Pending — new lifestyle images to be generated</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
           <t>Title calls this an 'Alabaster Marble Wall Sconce' but the body description never mentions alabaster or marble — it describes a 'frosted glass globe.' This looks like a title/description mismatch in the original listing; confirm with supplier whether the shade is genuine alabaster before including this SKU in the alabaster collection. | Live Etsy price as of 2026-07-08: Rs.31,852 sale (Rs.79,631 original) - differs from the USD estimate above; update once pricing stabilizes.</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -699,8 +708,10 @@
           <t>ALK-022</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>3</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -719,7 +730,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Genuine alabaster stone gives this double sconce its soft, warm glow, paired here with a solid brass structure finished in antique brass. Its unique natural patterns make each piece different from the last, and it's built to suit bathrooms, bedrooms, hallways, and living spaces. The fixture is UL listed and CE certified, dimmable with a compatible switch, and size, finish, or design can all be customized on request.</t>
+          <t>A handcrafted double wall sconce with a genuine alabaster shade and antique brass structure, UL listed and CE certified, and dimmer-switch compatible.Two alabaster shades on an antique brass frame give this sconce a fuller, more balanced spread of light than a single-shade fixture — ideal for bathrooms and hallways that need more than a single soft glow to feel properly lit. The antique brass finish adds a lived-in warmth from the start, rather than something that needs years to develop.Built to UL and CE safety standards, it's a piece you can install with real confidence, and pairing it with a dimmer switch or dimmable bulb lets you shift from a bright grooming light in the morning to a low, relaxed glow by evening.At 5"W x 11"H x 6"D, it holds its own on a bathroom or hallway wall without overwhelming the space. Fully customizable in size, finish, or design on request, and hand-assembled by ArtLoka's artisans in India — genuine alabaster character built into a certified, dependable fixture.Because it's built and tested to recognized electrical safety standards, it's a dependable choice for vacation properties, rentals, or hospitality projects that need certified, reliable lighting — without sacrificing the warm, handcrafted character that sets it apart from mass-produced fixtures.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -737,14 +748,20 @@
           <t>Genuine alabaster stone, solid brass</t>
         </is>
       </c>
-      <c r="J3" t="n">
-        <v>5</v>
-      </c>
-      <c r="K3" t="n">
-        <v>11</v>
-      </c>
-      <c r="L3" t="n">
-        <v>6</v>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -798,12 +815,17 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Pending — new lifestyle images to be generated</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
           <t>Bulb specification text in the source listing is garbled ('G9 Ex12 socket', 'G9 Ex14 socket') — interpreted here as G9/E12 (US) and G9/E14 (UK), but confirm exact socket types with supplier before publishing. | Live Etsy price as of 2026-07-08: Rs.23,943 sale (Rs.59,857 original) - differs from the USD estimate above; update once pricing stabilizes.</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -813,8 +835,10 @@
           <t>ALK-023</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>4</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -833,7 +857,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>This compact sconce diffuses light gently through a natural-textured stone shade set on a handcrafted metal frame, adding warmth and a distinctive flair wherever it's mounted. Its simple silhouette suits both contemporary and traditional interiors equally well, making it a versatile choice for bathroom vanities and bedside walls. Offered in seven finishes, from antique patina to polished chrome.</t>
+          <t>A compact wall sconce with a naturally textured stone-style shade on a handcrafted metal frame, offered in seven finishes.This is a smaller-scale piece built for spaces that want warmth without a large footprint — a naturally textured shade that diffuses light gently, mounted on a handcrafted metal frame available in seven finishes from antique patina to polished chrome. Its simple, unfussy silhouette means it sits comfortably in both contemporary and more traditional interiors.At just 5"W x 9"H, it tucks easily into bathroom vanities, bedside walls, or hallway runs where a larger sconce wouldn't fit as naturally, without giving up the warm, diffused glow that makes stone-shaded lighting so appealing.Handcrafted by ArtLoka's artisans in India, each shade carries slight natural variation in texture that only adds to its individual character — the kind of small imperfection that signals a piece was actually made by hand, not stamped out identically a thousand times over.Its compact scale and seven-finish flexibility make it an easy, low-commitment way to bring genuine handcrafted lighting into a rental, a guest room, or any smaller wall where a larger fixture simply wouldn't fit — proof that good design doesn't need to take up much space.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -851,14 +875,20 @@
           <t>Metal frame, alabaster-style stone shade</t>
         </is>
       </c>
-      <c r="J4" t="n">
-        <v>5</v>
-      </c>
-      <c r="K4" t="n">
-        <v>9</v>
-      </c>
-      <c r="L4" t="n">
-        <v>6</v>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -912,12 +942,17 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Pending — new lifestyle images to be generated</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
           <t>Source describes the shade as 'Alabaster-style' rather than genuine alabaster ('Stone / Alabaster Style' material listing) — confirm with supplier whether this is real alabaster or a faux-alabaster material before publishing under the alabaster collection. | Live Etsy price as of 2026-07-08: Rs.17,956 sale (Rs.44,889 original) - differs from the USD estimate above; update once pricing stabilizes.</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -927,8 +962,10 @@
           <t>ALK-025</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>5</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -947,7 +984,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>A softly sculpted alabaster shade sits on refined brass hardware in this sconce, its organic silhouette and warm glow creating a calming presence in modern, minimalist, and luxury interiors. Every shade is handcrafted from genuine alabaster, so the veining and texture are unique to each piece. Offered in seven brass finishes, and hand-finished throughout by our artisans.</t>
+          <t>A softly sculpted alabaster wall sconce on refined brass hardware, with an organic silhouette and a warm, calming glow.The shape here is deliberately organic — a softly sculpted alabaster form that feels more like a piece of natural stone worn smooth by time than a manufactured fixture. Mounted on refined brass hardware and available across seven finishes, it brings a genuinely calming quality to whatever room it's installed in.At 8"W x 14"H x 8"D, it has enough scale to anchor a bathroom, bedroom, or living room wall as a real design feature, while the organic form keeps it from ever feeling heavy-handed. The glow it casts is warm and even, filtered through genuine alabaster with all the natural veining that implies.Handmade and hand-finished by ArtLoka's artisans in India, no two shades are ever quite identical — a quality that turns a light fixture into something closer to a small piece of sculpture that happens to also light your room.Its organic form pairs particularly well with natural materials elsewhere in a room — think linen upholstery, raw wood furniture, or a stone countertop — making it a strong anchor piece for anyone building out an earthy, texture-forward interior.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -965,14 +1002,20 @@
           <t>Genuine alabaster stone, brass</t>
         </is>
       </c>
-      <c r="J5" t="n">
-        <v>8</v>
-      </c>
-      <c r="K5" t="n">
-        <v>14</v>
-      </c>
-      <c r="L5" t="n">
-        <v>8</v>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1026,12 +1069,17 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Pending — new lifestyle images to be generated</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
           <t>Title says 'Double Shade' but the description and dimensions describe a single-shade sconce with one canopy — confirm with supplier whether this is actually a double-shade fixture before repeating that claim on the website. | Live Etsy price as of 2026-07-08: Rs.23,725 sale (Rs.59,313 original) - differs from the USD estimate above; update once pricing stabilizes.</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1041,8 +1089,10 @@
           <t>ALK-026</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>6</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1061,7 +1111,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>A gentle arching mount in warm, distressed metalwork supports a rounded alabaster diffuser in this transitional sconce, turning an ordinary wall into a design statement. The fixture is UL listed and thoroughly tested before shipment, and can be customized with an added switch, a plug-in cord, or sloped-ceiling hardware on request. Its softly aged finish suits both traditional and modern-transitional interiors.</t>
+          <t>A transitional alabaster wall sconce with an arching, distressed-brass mount supporting a rounded diffuser, UL listed and tested before shipment.An arching brass mount, deliberately distressed for a worn-in warmth, curves out from the wall to support a rounded alabaster diffuser — the kind of quiet architectural gesture that turns an ordinary wall into a genuine design moment. It's a piece that sits comfortably between traditional and modern, which is exactly what transitional style is meant to do.Built to UL standards and tested prior to shipment, it's ready to install with confidence, and can be further customized with an added switch, a plug-in cord conversion, or hardware for sloped ceilings depending on how your space is wired.At 5"W x 9.25"H x 8.375"D, it's a substantial enough piece to work as a genuine bathroom or hallway accent rather than a filler light. Handmade by ArtLoka's artisans in India, with the same natural stone variation that makes every alabaster shade a little different from the last.Its transitional styling makes it one of the more adaptable pieces in the collection — equally comfortable flanking a clawfoot tub in a vintage-inspired bathroom or lighting a hallway in a more contemporary home that just wants a touch of warmth and history.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1079,14 +1129,20 @@
           <t>Alabaster, distressed brass</t>
         </is>
       </c>
-      <c r="J6" t="n">
-        <v>5</v>
-      </c>
-      <c r="K6" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="L6" t="n">
-        <v>8.375</v>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>9.25</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>8.375</t>
+        </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1140,12 +1196,17 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Pending — new lifestyle images to be generated</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
           <t>Title calls this a 'Double Wall Sconce' but the description and dimensions describe a single rounded diffuser — confirm with supplier before repeating 'double' on the website. Header states Height 9.5in while the detailed Dimensions section says 9.25in — minor conflict, verify. Bulb type (E26/E27 medium base) differs from the G9/E12 pattern used by most other alabaster SKUs — confirm this is correct for this specific listing. | Live Etsy price as of 2026-07-08: Rs.35,600 sale (Rs.88,999 original) - differs from the USD estimate above; update once pricing stabilizes.</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1155,8 +1216,10 @@
           <t>ALK-027</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>7</v>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1175,7 +1238,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Twin arched brackets support clean-lined shades in this antique brass sconce, softly illuminating every detail with classic charm. The sleek curved arm and minimalist styling suit modern, mid-century, Art Deco, and luxury interiors alike, and it works equally well as bedside reading light, a hallway accent, or a statement bathroom fixture. UL listed and hand-finished, with each shade carrying its own natural veining.</t>
+          <t>ArtLoka's Twin-Bracket Wall Sconce pairs an antique brass frame with clean-lined stone shades, for a classic, softly illuminated glow.Twin arched brackets reach out symmetrically from the wall, each cradling a clean-lined stone shade that glows with a soft, classic warmth reminiscent of old-world sconces. The antique brass finish leans into that vintage feeling from day one, while the curved arms and minimalist shades keep the overall look from feeling dated.It's a versatile piece — equally comfortable in an Art Deco-inspired bedroom, a mid-century hallway, or a more traditional bathroom vanity — and the double-shade design gives a fuller spread of light than a single sconce would.At 5"W x 10"H x 5"D, it holds real presence on a wall without overwhelming the space, and it's built to UL standards and tested prior to shipment. Handmade by ArtLoka's artisans in India, each shade carrying its own natural character — a classic silhouette with the small imperfections that only genuine handmade work can offer.Because the twin brackets give a fuller spread of light than a single-shade sconce, it works well anywhere you need genuine illumination alongside ambiance — a vanity that needs real task light, or a hallway that's a little too dim for a single softer fixture.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1193,14 +1256,20 @@
           <t>Alabaster, antique brass</t>
         </is>
       </c>
-      <c r="J7" t="n">
-        <v>5</v>
-      </c>
-      <c r="K7" t="n">
-        <v>10</v>
-      </c>
-      <c r="L7" t="n">
-        <v>5</v>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1254,12 +1323,17 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Pending — new lifestyle images to be generated</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
           <t>Source lists material as 'alabaster, brass' up top, but the Features section separately describes 'Genuine white marble shade' — confirm with supplier whether the shade is alabaster or white marble before publishing. Description text is also near-identical to ALK-029 (4525491364) apart from title — verify these are genuinely distinct listings. | Live Etsy price as of 2026-07-08: Rs.19,576 sale (Rs.48,941 original) - differs from the USD estimate above; update once pricing stabilizes.</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1269,8 +1343,10 @@
           <t>ALK-028</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>8</v>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1289,7 +1365,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Premium alabaster marble meets a refined brushed brass finish in this minimalist cone-shaped sconce, built to bring warm ambient lighting to hallways, bathrooms, bedsides, and living rooms. The natural stone veining shows through beautifully in the brushed finish, and the fixture ships with a flush mount canopy included. It can be wired as hardwired or plug-in on request, and is handmade start to finish by our artisans.</t>
+          <t>A minimalist cone-shaped alabaster sconce in a brushed brass finish, bringing warm ambient light to hallways, bathrooms, and bedsides.The cone shape here is deceptively simple — a clean, tapered silhouette that lets the alabaster's natural veining show through the brushed brass finish without any extra ornamentation getting in the way. It's minimalism done warmly, rather than starkly, thanks to the stone's soft diffusion.At 6"W x 14"H x 6"D, it's sized to work as a genuine hallway or bedside accent, and the flush mount canopy that ships with it means installation stays clean and unfussy. Wiring flexibility is built in too — order it hardwired for a permanent install, or request a plug-in version if you'd rather avoid opening up the wall.Handmade and hand-finished by ArtLoka's artisans in India, this sconce is a good entry point into the collection for anyone who wants genuine alabaster warmth without a lot of visual complexity — quiet, considered, and built to last.The choice between hardwired and plug-in installation makes it especially easy to place — commit to a permanent wall fixture in a finished room, or use the plug-in version as a renter-friendly accent that still delivers genuine alabaster warmth without any electrical work.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1307,14 +1383,20 @@
           <t>Alabaster marble, solid brass</t>
         </is>
       </c>
-      <c r="J8" t="n">
-        <v>6</v>
-      </c>
-      <c r="K8" t="n">
-        <v>14</v>
-      </c>
-      <c r="L8" t="n">
-        <v>6</v>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1368,12 +1450,17 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Pending — new lifestyle images to be generated</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
           <t>None significant — dimensions and bulb specs are internally consistent within this listing. | Live Etsy price as of 2026-07-08: Rs.21,972 sale (Rs.54,931 original) - differs from the USD estimate above; update once pricing stabilizes.</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1383,8 +1470,10 @@
           <t>ALK-029</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>9</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1403,7 +1492,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Twin arched brackets support clean-lined shades in this antique brass sconce, softly illuminating every detail with classic charm. The sleek curved arm and minimalist styling suit modern, mid-century, Art Deco, and luxury interiors, working equally well as bedside reading light, a hallway accent, or a bathroom fixture. UL listed and hand-finished, with each shade carrying its own natural veining.</t>
+          <t>A classic wall sconce with twin arched brackets and softly glowing stone shades, for a warm, symmetrical accent on any wall.Twin arched brackets mirror each other across this sconce's antique brass frame, each cradling a clean-lined stone shade that diffuses light into a soft, old-world glow. It's a design that leans classic without feeling stuck in the past — equally suited to an Art Deco bedroom, a mid-century hallway, or a more traditional bathroom.The double-shade layout gives a fuller spread of light than a single sconce, which makes it a strong choice anywhere you want genuine illumination alongside the ambiance — a bedside pairing, a hallway accent, or a statement piece by the bathtub.At 5"W x 10"H x 5"D and built to UL standards, it's ready to install with confidence. Handmade by ArtLoka's artisans in India, with each stone shade carrying its own natural veining — the small, honest variation that separates genuine handmade lighting from anything mass-produced.Like its twin-bracket sibling, the fuller spread of light from two shades makes this a practical pick anywhere ambiance alone isn't quite enough — a vanity, a stairwell, or a hallway that benefits from both genuine brightness and a warm, classic glow.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1421,14 +1510,20 @@
           <t>Alabaster, antique brass</t>
         </is>
       </c>
-      <c r="J9" t="n">
-        <v>5</v>
-      </c>
-      <c r="K9" t="n">
-        <v>10</v>
-      </c>
-      <c r="L9" t="n">
-        <v>5</v>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1482,12 +1577,1033 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Pending — new lifestyle images to be generated</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
           <t>IMPORTANT: Title references a 'Brass Chain Pendant Light' but the sourced description is near-identical boilerplate to ALK-027 (4527129047) describing a twin-bracket wall sconce — no chain or pendant is mentioned anywhere in the body text. This is a significant title/description mismatch; verify the actual product with the supplier before publishing, as this may be a mislabeled or duplicate listing. | Live Etsy price as of 2026-07-08: Rs.23,725 sale (Rs.59,313 original) - differs from the USD estimate above; update once pricing stabilizes.</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ALK-001</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Genuine Alabaster Stone Brass Wall Sconce | Art Deco Vanity Light, Luxury Home Lighting</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Alabaster &amp; Brass Wall Sconce | Art Deco Vanity Light – ArtLoka</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Handcrafted alabaster &amp; brass wall sconce with an Art Deco silhouette. Genuine stone veining and a warm ambient glow, artisan-made in India.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>At ArtLoka, this Art Deco-inspired wall sconce pairs genuine alabaster stone with solid, heavy-duty brass for a fixture that feels as luxurious as it looks. Each stone shade is hand-selected and hand-finished by our artisans, so the natural veining running through the alabaster is never quite the same twice. Mounted, it casts a soft, warm, diffused glow that works beautifully as bedside lighting, a hallway accent, or a statement piece in a dining room or entryway. Unlike lacquered or brass-coated alternatives, we use unlacquered solid brass so the finish only deepens with age. Available in seven brass finishes to match your existing hardware, from raw brass to blackened brass and polished chrome.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.etsy.com/in-en/listing/4534999887/alabaster-stone-brass-wall-sconce-art</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>$499.67</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Genuine alabaster stone, solid brass</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Round backplate, 5" dia. (approx.)</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Raw brass, Polished brass, Antique patina, Brushed chrome, Polished chrome, Blackened brass, Black matte</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>1 x G9 bi-pin, 120V (bulb not included)</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>1 x G9 bi-pin, 240V (bulb not included)</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Art Deco, Luxury, Vanity</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Bedroom, living room, hallway, dining room, hotel/hospitality interiors</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>UL-listed components, all mounting hardware included, hand-finished natural stone (slight variation is normal)</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Handmade &amp; hand-finished by ArtLoka artisans in India</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>alabaster sconce, brass wall sconce, art deco light, luxury sconce, bedside wall lamp, handmade brass lamp, antique brass sconce, marble wall light, luxury home light, hotel wall sconce, alabaster lamp, unlacquered brass</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>alabaster wall sconce, brass wall sconce, art deco wall light, genuine alabaster lighting, handmade brass wall light, luxury vanity sconce, unlacquered brass sconce, artisan alabaster lamp</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Etsy meta price tag ($499.67) doesn't reconcile cleanly with displayed INR price at ~83 INR/USD — verify live price before publishing. | Live Etsy price as of 2026-07-09: Rs.19,812 sale (Rs.49,531 original) - differs from the USD estimate above; update once pricing stabilizes.</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ALK-030</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Handmade Brass Wall Sconce with Alabaster Shade – Mid Century Lighting</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>French Country Brass Wall Sconce | Scalloped Glass – ArtLoka</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Handcrafted antique brass wall sconce with scalloped glass shade. French country styling for bedrooms and reading nooks. Made in India.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Inspired by French country and vintage European design, this handcrafted sconce pairs a graceful curved arm in antique brass with a delicate, flower-inspired scalloped glass shade. It creates a warm, inviting glow suited to bedrooms, hallways, bathrooms, reading nooks, and cottage-style living spaces. As with every ArtLoka piece, it's handmade and hand-finished for lasting character.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.etsy.com/in-en/listing/4534964188/handmade-brass-wall-sconce-with</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>$541.65</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Brass, scalloped glass shade</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>9.4</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Not specified — confirm with supplier</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Antique brass</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>1 x E26/E27 (bulb not included)</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>1 x E26/E27 (bulb not included)</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>French Country, Farmhouse, Traditional</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Bedroom, hallway, bathroom, reading nook, living room</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Curved decorative arm, scalloped glass shade, hardwired installation, suitable for cottage/farmhouse interiors</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Handmade &amp; hand-finished by ArtLoka artisans in India</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>country wall sconce, antique brass light, scalloped glass, farmhouse wall lamp, cottage wall light, vintage european, reading nook lamp, bedroom wall sconce, hallway wall light, handmade brass, traditional lamp, curved arm sconce, luxury bedroom light</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>french country wall sconce USA, antique brass scalloped light UK, farmhouse bedroom lamp, cottage wall sconce, vintage brass wall light</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>IMPORTANT: Title says 'Alabaster Shade' but the description explicitly describes 'a beautiful white scalloped glass shade' with French-country styling — no alabaster is mentioned; live listing body text confirms 'Materials: Brass, Glass'. Confirm with supplier whether this SKU actually belongs in the alabaster collection before publishing. | Live Etsy price as of 2026-07-09: Rs.27,668 sale (Rs.69,171 original) - differs from the USD estimate above; update once pricing stabilizes.</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ALK-031</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Solid Brass Alabaster Cylinder Sconce, Mid Century Modern Wall Light Fixture</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Solid Brass Alabaster Cylinder Wall Sconce | ArtLoka</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Tall solid brass alabaster cylinder sconce, seven finishes. Warm ambient glow for bedrooms, hallways and hotel interiors. Made in India.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>A French country-inspired antique brass wall sconce with a curved arm and a delicate scalloped glass shade, for a warm, vintage-styled glow.There's a softness to this sconce that feels distinctly European — a graceful curved arm in antique brass supporting a scalloped glass shade shaped like an unfurling flower. It's the kind of detail that turns a light fixture into a decorative moment, well suited to cottage, farmhouse, and traditional interiors that lean into texture and warmth over hard lines.At 5.5"W x 9"H x 9.4"D, it has enough presence to work as a real accent piece in a reading nook, bedroom, or hallway, casting a warm, inviting glow that feels more like a vintage lamp than a modern fixture.Handmade by ArtLoka's artisans in India, this sconce is a gentle nod to French country and vintage European design — proof that a wall light can carry as much character and craft as any other piece of furniture in the room.Its scalloped glass shade and curved arm make it a particularly good fit for a cottage-style bedroom, a farmhouse hallway, or any reading nook that wants a touch of old-world romance alongside genuinely warm, flattering light.It's a fitting choice for anyone drawn to old-world antique styling, brought home to a modern setting without losing that charm.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.etsy.com/in-en/listing/4534971738/solid-brass-alabaster-cylinder-sconce</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>$502.86</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Alabaster, pure brass</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>5" diameter</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Polished brass, Brushed brass, Polished chrome, Antique black, Raw brass, Blackened brass, Antique patina</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>1 x E12, 120V (bulb not included)</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>1 x G9, 240V (bulb not included)</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Mid-Century Modern</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Bedroom, living room, hallway, entryway, bathroom, hotel interiors</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>UL approved (US), CE certified (Europe), free customization available (size/finish/design), tall cylinder silhouette</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Handmade &amp; hand-finished by ArtLoka artisans in India</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>alabaster cylinder, solid brass light, century wall lamp, tall wall sconce, handmade brass, luxury wall light, hallway wall lamp, bedroom wall sconce, hotel wall lighting, UL listed sconce, CE certified light, artisan alabaster, seven finish sconce</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>solid brass alabaster cylinder sconce USA, tall wall sconce UK, mid century brass wall lamp, hotel wall lighting fixture, handmade cylinder sconce</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>None significant — dimensions and finish options are internally consistent within this listing. | Live Etsy price as of 2026-07-09: Rs.25,812 sale (Rs.64,531 original) - differs from the USD estimate above; update once pricing stabilizes.</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ALK-021</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Alabaster Stone Wall Sconce, Natural Marble Light, Mid Century Modern Brass Lamp</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Alabaster Sphere Wall Sconce | Mid-Century Brushed Brass – ArtLoka</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Alabaster sphere wall sconce in brushed brass, custom sphere sizes 8-18in. Soft glow for bedrooms, bathrooms and hotel interiors.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>An alabaster sphere wall sconce on a brushed brass base, offered in a range of sphere sizes for a clean, modern glow.A softly glowing alabaster sphere is the whole idea behind this sconce — a simple, confident shape mounted on a brushed brass base that gets out of the way and lets the stone do the work. Light filters through the sphere evenly in every direction, giving a rounder, gentler glow than a flat-shaded fixture.What sets this piece apart is scale flexibility: the sphere is available from 8 to 18 inches in diameter, so the same considered design can work as a subtle bedside accent or a genuine architectural statement, depending on the size you choose for your space.Suited to bedrooms, hallways, bathrooms, and living rooms — and just as much at home in a boutique hotel as a private residence — this sconce is handcrafted by ArtLoka's artisans in India, with each alabaster sphere individually shaped and finished, so no two spheres ever glow in quite the same way.The size range is what really sets this piece apart — order the 8-inch sphere for a subtle bedside glow, or go all the way to 18 inches for a genuine architectural statement in a double-height entryway or great room, all from the same considered design.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.etsy.com/in-en/listing/4534973463/alabaster-stone-wall-sconce-natural</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>$464.23</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Solid brass, alabaster</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>5" diameter</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Antique, Polished, Matte black (customizable on request)</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>1 x E26/E27 (bulb not included)</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>1 x E26/E27 (bulb not included)</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Modern, Minimalist, Contemporary</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Bedroom, hallway, living room, bathroom, hotel interiors</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Sphere shade available in 8"-18" diameters, custom sizing and finishes on request, hardwired installation</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Handmade &amp; hand-finished by ArtLoka artisans in India</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>alabaster sphere, natural marble light, brushed brass sconce, century wall lamp, bathroom vanity, custom size sconce, luxury wall light, hallway wall sconce, hotel wall lighting, modern globe sconce, handmade brass lamp, contemporary light, sphere wall lamp</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>alabaster sphere wall sconce USA, brushed brass globe light UK, custom size alabaster sconce, mid century sphere lamp, hotel wall lighting fixture</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Source lists overall Width/Height as 10"x10" while also stating the disc diameter can range from 8" to 18" (custom) — clarify which dimension is the standard/default size for this SKU before publishing (the 10" disc is used here as the default). | Live Etsy price as of 2026-07-09: Rs.23,732 sale (Rs.59,331 original) - differs from the USD estimate above; update once pricing stabilizes.</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ALK-002</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Handmade Alabaster Brass Wall Sconce | Modern Minimalist Ambient Lighting</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Handmade Alabaster &amp; Brass Wall Sconce | Modern Minimalist – ArtLoka</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Ruffled tulip-bell alabaster wall sconce with hand-finished brass hardware. A soft ambient glow for bedrooms, hallways &amp; living rooms.</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ArtLoka's Ruffled Tulip-Bell Wall Sconce pairs a scalloped, flower-like alabaster shade with a compact brass ball-joint stem for a softer kind of warmth.Rather than a plain cone or cylinder, this sconce's shade takes on an organic, ruffled form — a tulip-bell silhouette with a scalloped, petal-like edge that catches the light differently along each curve. It's a small departure from the more architectural pieces in ArtLoka's collection, and one that brings a gentler, more romantic character to a wall.The compact ball-joint stem keeps the footprint small, making it a natural fit for bedside reading light, a hallway run, or a softly lit accent on a living room wall where space is at a premium. Every shade is hand-selected and hand-finished, so the alabaster's natural veining is genuinely one of a kind, and the fixture pairs easily with a dimmer switch or dimmable bulb for full control over the mood.Available across seven brass finishes, including antique patina and brushed chrome, it's a considered, slightly whimsical addition to a room that wants warmth without losing its clean lines.It also makes a thoughtful gift for anyone furnishing a first home or refreshing a reading nook, since it brings genuine handmade character without asking for a lot of wall space in return.</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.etsy.com/in-en/listing/4535005962/handmade-alabaster-brass-wall-sconce</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>$499.78</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Alabaster, brass (listing highlights also reference marble)</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>5" diameter canopy</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Raw brass, Polished brass, Antique patina, Brushed brass, Brushed chrome, Polished chrome, Blackened brass, Black matte</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>1 x E12, 120V (bulb not included)</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>1 x G9, 240V (bulb not included)</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Modern, Minimalist</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Bedroom, hallway, living room, bedside</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Compatible with dimmer switches, UL-listed components, easy install with included hardware</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Handmade by skilled ArtLoka artisans</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>alabaster sconce, brass wall light, tulip bell sconce, handmade wall lamp, ruffled alabaster, bedside brass light, hallway wall sconce, ambient wall light, brass bedroom lamp, alabaster lighting, brushed brass sconce, small wall sconce, scalloped light</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>modern alabaster wall sconce, minimalist brass wall light, handmade dimmable sconce, brass bedside lamp, alabaster ambient lighting</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Listing text claims 'Indoor &amp; Outdoor' use — flag for review; natural alabaster is porous and not typically weather-rated, recommend confirming before repeating this claim. Also: source Etsy title says 'Modern Minimalist' but the actual reference photo shows a ruffled/scalloped tulip-bell shade, not a plain minimalist silhouette — website description above matches the photo, not the original Etsy title. | Live Etsy price as of 2026-07-09: Rs.19,732 sale (Rs.49,331 original) - differs from the USD estimate above; update once pricing stabilizes.</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ALK-003</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Modern Alabaster Wall Light, Brass Bedside Sconce</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Modern Alabaster Wall Light | Brass Bedside Sconce – ArtLoka</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Tall alabaster and solid brass bedside sconce, made to order and hand-finished by artisans. A soft, warm glow for bedrooms and hallways.</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Designed for bedside reading and soft evening light, this ArtLoka sconce combines natural alabaster marble with solid brass for a fixture that reads as both modern and enduring. Its taller profile makes it a striking option for hallway runs or as a pair flanking a headboard. Each piece is made to order and hand-finished, so slight variations in the stone's color and texture are part of its charm rather than a flaw. Compatible with dimmable LED bulbs, and finished in your choice of eight brass tones.</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.etsy.com/in-en/listing/4536290360/modern-alabaster-wall-light-brass</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>$549.78</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Natural alabaster marble, solid brass</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>5" diameter canopy</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Raw brass, Polished brass, Antique patina, Blackened brass, Brushed chrome, Polished chrome, Brushed brass, Black matte</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>1 x E26, 120V (bulb not included)</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>1 x E14, 240V (bulb not included)</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Modern, Minimalist, Luxury</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Bedroom (bedside), hallway</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Made to order (ships in 5-7 days), compatible with LED &amp; dimmable bulbs, natural stone variation is normal and expected</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Handmade by skilled ArtLoka artisans</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>alabaster bedside, brass wall light, modern alabaster, luxury bedside light, minimalist sconce, made to order lamp, dimmable sconce, tall wall sconce, hallway pair lights, marble bedside lamp, brass reading light, alabaster marble, bedroom light</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>alabaster bedside sconce, brass wall light, modern bedside wall lamp, luxury alabaster lighting, made-to-order wall sconce</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Approved (8 images in Drive folder 15)</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Catalog note: Socket spec differs from ALK-001/002 (E26 US / E14 UK vs G9/E12) — confirm correct bulb type before publishing. | Live Etsy price 2026-07-12: Rs.21,732 sale (Rs.54,331 original), 60% off, sale ends 05 Aug 2026. | Relisted under new Etsy ID 4536290360 (catalog had older ID 4513956333).</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>New — ready for website</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ALK-004</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Alabaster Double Wall Sconce, Antique Brass Modern Lamp</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Alabaster Double Wall Sconce | Antique Brass Statement Lamp – ArtLoka</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Double-shade alabaster wall sconce in antique brass, with decorative sphere accents. Balanced, warm illumination for modern or vintage-inspired homes.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>A statement piece for anyone who wants a little more presence on the wall, this double alabaster sconce from ArtLoka pairs two genuine stone shades with an antique brass frame and decorative sphere accents. The dual shades give a more balanced spread of light than a single sconce, making it a favorite for bathrooms, hallways, and living areas that need a bit more glow. As with every ArtLoka piece, it's handmade and hand-finished, so no two sconces are quite identical. Choose a regular or flush backplate depending on your wall setup, and pick from seven brass finishes.</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.etsy.com/in-en/listing/4536296108/alabaster-double-wall-sconce-antique</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>$549.78</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Alabaster marble shades, natural marble spheres, solid brass body</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Regular or Flush backplate options</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Raw brass, Antique patina, Brushed brass, Polished brass, Brushed chrome, Polished chrome, Black matte</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>1 x E12, 120V (bulb not included)</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>1 x G9 bi-pin, 240V (bulb not included)</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Mid-Century Modern, Double Sconce</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Bathroom, hallway, bedroom, living room</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Decorative sphere accents, double-shade balanced illumination, UL-listed hardware, all mounting hardware included</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Handmade &amp; hand-finished by ArtLoka artisans</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>double wall sconce, alabaster double, antique brass sconce, brass wall lamp, century wall light, bathroom sconce, hall double sconce, marble sphere sconce, statement light, two light sconce, brass sphere lamp, brass fixture, decorative sconce</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>double alabaster wall sconce, antique brass double light, mid-century wall sconce, bathroom alabaster sconce, brass sphere wall lamp</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Approved (7 images in Drive folder 16)</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Catalog note: None significant — dimensions and specs internally consistent. | Live Etsy highlights show Depth 16in but body text and catalog state 6in — using 6in; confirm. | Live Etsy price 2026-07-12: Rs.21,732 sale (Rs.54,331 original), 60% off, sale ends 05 Aug 2026. | Relisted under new Etsy ID 4536296108 (catalog had older ID 4512430965).</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>New — ready for website</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ALK-005</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Handmade Brass Double Sconce with Alabaster Shades</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Handmade Brass Double Sconce with Alabaster Shades – ArtLoka</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Compact double-shade brass sconce with natural alabaster diffusers. Customizable finish, vertical or horizontal mount, artisan-made.</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>This compact double sconce brings a quiet-luxury feel to smaller wall spaces. Two natural alabaster shades diffuse the light softly, while the solid brass frame keeps the silhouette sleek enough for modern, mid-century, or minimalist interiors alike. It's a versatile piece — mount it vertically or horizontally, and customize the stone color or add a leather wrap on request. Every shade is naturally unique, with its own subtle veining, so each fixture carries a bit of one-of-a-kind character.</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.etsy.com/in-en/listing/4536303548/handmade-brass-double-sconce-with</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>$549.78</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Alabaster, brass</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2.25" diameter shade (per product detail section)</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Raw brass, Brushed brass, Antique patina, Polished brass, Brushed chrome, Polished chrome, Black matte</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>E12/E26 socket, 110-120V (bulb not included)</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>E14/E27 socket, 220-250V (bulb not included)</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Minimalist</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Bathroom, bedroom, hallway, vanity/bedside</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Customizable stone color or leather wrap on request, mountable vertically or horizontally, compatible with dimmable bulbs</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Handmade by Indian artisans</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>double alabaster, brass wall lamp, compact wall sconce, minimalist brass, vanity double sconce, custom wall sconce, quiet luxury light, small brass sconce, leather brass lamp, alabaster vanity, bathroom double, handmade brass, modern minimalist</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>compact double wall sconce, brass alabaster vanity light, customizable brass sconce, minimalist double wall lamp, quiet luxury lighting</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Approved (9 images in Drive folder 17)</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Catalog note: Dimensions conflict in original listing — highlights 3"W x 12"H x 5"D vs product-details Height 10in / Width 2.25in / Diameter 2.25in; confirm actual dims with supplier. | Live Etsy price 2026-07-12: Rs.21,732 sale (Rs.54,331 original), 60% off, sale ends 05 Aug 2026. | Relisted under new Etsy ID 4536303548 (catalog had older ID 4511703701).</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>New — ready for website</t>
         </is>
       </c>
     </row>
@@ -1502,46 +2618,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F90"/>
+  <dimension ref="A1:H171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Image URL</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Image Type</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Alt Text</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Sort Order</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Approved</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Listing Status</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Aspect Ratio</t>
         </is>
       </c>
     </row>
@@ -1566,12 +2694,24 @@
           <t>ArtLoka alabaster disc wall sconce with brass ball drop, lit, on a dark charcoal accent wall with brass elephant figurines</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>1</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1:1</t>
         </is>
       </c>
     </row>
@@ -1596,12 +2736,24 @@
           <t>Alabaster disc wall sconce shown across seven finish options: Antique Patina, Raw Brass, Blackened Brass, Antique Black, Polished Chrome, Polished Brass, Brushed Brass</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>2</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>1:1</t>
         </is>
       </c>
     </row>
@@ -1626,12 +2778,24 @@
           <t>Alabaster disc wall sconce mounted on a textured concrete wall in a modern living room</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>3</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>1:1</t>
         </is>
       </c>
     </row>
@@ -1656,12 +2820,24 @@
           <t>Three alabaster disc wall sconces lighting a staircase wall at dusk</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>4</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1:1</t>
         </is>
       </c>
     </row>
@@ -1686,12 +2862,24 @@
           <t>Three alabaster disc wall sconces along a stucco stairway wall with warm ambient glow</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>5</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>1:1</t>
         </is>
       </c>
     </row>
@@ -1716,12 +2904,24 @@
           <t>Alabaster disc wall sconce on a concrete wall beside a potted fig tree</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>6</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1:1</t>
         </is>
       </c>
     </row>
@@ -1746,12 +2946,24 @@
           <t>Close-up of alabaster disc wall sconce switched off, showing natural stone veining and brass ball drop</t>
         </is>
       </c>
-      <c r="E8" t="n">
-        <v>7</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>1:1</t>
         </is>
       </c>
     </row>
@@ -1776,12 +2988,24 @@
           <t>Alabaster disc wall sconce glowing warm on a dark wall beside a vintage candle holder and books</t>
         </is>
       </c>
-      <c r="E9" t="n">
-        <v>8</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1:1</t>
         </is>
       </c>
     </row>
@@ -1806,12 +3030,24 @@
           <t>Alabaster disc wall sconce close-up on a neutral putty-grey wall</t>
         </is>
       </c>
-      <c r="E10" t="n">
-        <v>9</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>1:1</t>
         </is>
       </c>
     </row>
@@ -1836,12 +3072,24 @@
           <t>Pair of alabaster disc wall sconces lighting a dark stairwell at night</t>
         </is>
       </c>
-      <c r="E11" t="n">
-        <v>10</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1:1</t>
         </is>
       </c>
     </row>
@@ -1866,12 +3114,24 @@
           <t>Alabaster disc wall sconce mounted on walnut wood paneling beside a mustard sofa and fiddle-leaf fig</t>
         </is>
       </c>
-      <c r="E12" t="n">
-        <v>11</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>3:4</t>
         </is>
       </c>
     </row>
@@ -1896,12 +3156,24 @@
           <t>Alabaster disc wall sconce beside a round brass-framed mirror in a bedroom</t>
         </is>
       </c>
-      <c r="E13" t="n">
-        <v>12</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>3:4</t>
         </is>
       </c>
     </row>
@@ -1926,12 +3198,24 @@
           <t>Alabaster disc wall sconce above a wooden entryway bench with a woven basket of eucalyptus</t>
         </is>
       </c>
-      <c r="E14" t="n">
-        <v>13</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>3:4</t>
         </is>
       </c>
     </row>
@@ -1956,12 +3240,24 @@
           <t>Alabaster disc wall sconce mounted beside a bathroom mirror and vanity</t>
         </is>
       </c>
-      <c r="E15" t="n">
-        <v>14</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>3:4</t>
         </is>
       </c>
     </row>
@@ -1986,12 +3282,24 @@
           <t>Alabaster disc wall sconce shown in polished brass and polished chrome finishes side by side</t>
         </is>
       </c>
-      <c r="E16" t="n">
-        <v>15</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>1:1</t>
         </is>
       </c>
     </row>
@@ -2016,12 +3324,24 @@
           <t>Alabaster disc wall sconce lighting a sage-green staircase landing</t>
         </is>
       </c>
-      <c r="E17" t="n">
-        <v>16</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>3:4</t>
         </is>
       </c>
     </row>
@@ -2046,12 +3366,24 @@
           <t>Alabaster disc wall sconce mounted above a marble bathroom vanity with a folded white towel</t>
         </is>
       </c>
-      <c r="E18" t="n">
-        <v>17</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>3:4</t>
         </is>
       </c>
     </row>
@@ -2076,12 +3408,24 @@
           <t>Pair of fluted alabaster double-globe wall sconces flanking a bathroom vanity mirror</t>
         </is>
       </c>
-      <c r="E19" t="n">
-        <v>1</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>5:4</t>
         </is>
       </c>
     </row>
@@ -2106,12 +3450,24 @@
           <t>Alabaster double-globe wall sconce shown across seven finish options: Antique Patina, Raw Brass, Blackened Brass, Antique Black, Polished Chrome, Polished Brass, Brushed Brass</t>
         </is>
       </c>
-      <c r="E20" t="n">
-        <v>2</v>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2:1</t>
         </is>
       </c>
     </row>
@@ -2136,12 +3492,24 @@
           <t>Fluted alabaster double-globe wall sconce beside a bed with linen pillows</t>
         </is>
       </c>
-      <c r="E21" t="n">
-        <v>3</v>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>4:5</t>
         </is>
       </c>
     </row>
@@ -2166,12 +3534,24 @@
           <t>Fluted alabaster double-globe wall sconce glowing on a dark wood-paneled wall beside a nightstand and laptop</t>
         </is>
       </c>
-      <c r="E22" t="n">
-        <v>4</v>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>4:5</t>
         </is>
       </c>
     </row>
@@ -2196,12 +3576,24 @@
           <t>Fluted alabaster double-globe wall sconce mounted beside a bathroom mirror and vanity</t>
         </is>
       </c>
-      <c r="E23" t="n">
-        <v>5</v>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>4:3</t>
         </is>
       </c>
     </row>
@@ -2226,12 +3618,24 @@
           <t>Fluted alabaster double-globe wall sconce lighting a warm hallway at dusk</t>
         </is>
       </c>
-      <c r="E24" t="n">
-        <v>6</v>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>4:5</t>
         </is>
       </c>
     </row>
@@ -2256,12 +3660,24 @@
           <t>Fluted alabaster double-globe wall sconce glowing against a dark charcoal wall</t>
         </is>
       </c>
-      <c r="E25" t="n">
-        <v>7</v>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>4:5</t>
         </is>
       </c>
     </row>
@@ -2286,12 +3702,24 @@
           <t>Fluted alabaster double-globe wall sconce shown across seven finish options in a horizontal layout</t>
         </is>
       </c>
-      <c r="E26" t="n">
-        <v>8</v>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>1:1</t>
         </is>
       </c>
     </row>
@@ -2316,12 +3744,24 @@
           <t>Fluted alabaster double-globe wall sconce beside a bathroom mirror with reflected vanity</t>
         </is>
       </c>
-      <c r="E27" t="n">
-        <v>9</v>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>4:3</t>
         </is>
       </c>
     </row>
@@ -2346,12 +3786,24 @@
           <t>Pair of fluted alabaster double-globe wall sconces flanking a bathroom mirror with reflection</t>
         </is>
       </c>
-      <c r="E28" t="n">
-        <v>10</v>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>4:3</t>
         </is>
       </c>
     </row>
@@ -2376,12 +3828,24 @@
           <t>Fluted alabaster double-globe wall sconce, warm lit, on a plain neutral wall</t>
         </is>
       </c>
-      <c r="E29" t="n">
-        <v>11</v>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>1:1</t>
         </is>
       </c>
     </row>
@@ -2406,12 +3870,24 @@
           <t>Gooseneck alabaster cylinder wall sconce beside a bedroom nightstand with books and a coffee cup</t>
         </is>
       </c>
-      <c r="E30" t="n">
-        <v>1</v>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>9:8</t>
         </is>
       </c>
     </row>
@@ -2436,12 +3912,24 @@
           <t>Gooseneck alabaster cylinder wall sconce lighting a wood-paneled home office with bookshelves</t>
         </is>
       </c>
-      <c r="E31" t="n">
-        <v>2</v>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>9:8</t>
         </is>
       </c>
     </row>
@@ -2466,12 +3954,24 @@
           <t>Gooseneck alabaster cylinder wall sconce glowing against a dark charcoal wall</t>
         </is>
       </c>
-      <c r="E32" t="n">
-        <v>3</v>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>9:8</t>
         </is>
       </c>
     </row>
@@ -2496,12 +3996,24 @@
           <t>Gooseneck alabaster cylinder wall sconce shown across seven finish options on a wood-plank wall</t>
         </is>
       </c>
-      <c r="E33" t="n">
-        <v>4</v>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>9:8</t>
         </is>
       </c>
     </row>
@@ -2526,12 +4038,24 @@
           <t>Gooseneck alabaster cylinder wall sconce, warm lit, on a plain neutral wall</t>
         </is>
       </c>
-      <c r="E34" t="n">
-        <v>5</v>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>9:8</t>
         </is>
       </c>
     </row>
@@ -2556,12 +4080,24 @@
           <t>Gooseneck alabaster cylinder wall sconce lighting a teal dining room wall beside a set table</t>
         </is>
       </c>
-      <c r="E35" t="n">
-        <v>6</v>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>9:8</t>
         </is>
       </c>
     </row>
@@ -2586,12 +4122,24 @@
           <t>Double-goblet alabaster wall sconce lighting a bright living room seating area</t>
         </is>
       </c>
-      <c r="E36" t="n">
-        <v>1</v>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>4:5</t>
         </is>
       </c>
     </row>
@@ -2616,12 +4164,24 @@
           <t>Double-goblet alabaster wall sconce glowing beside a bathroom mirror at night</t>
         </is>
       </c>
-      <c r="E37" t="n">
-        <v>2</v>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>4:5</t>
         </is>
       </c>
     </row>
@@ -2646,12 +4206,24 @@
           <t>Double-goblet alabaster wall sconce glowing against a dark charcoal wall</t>
         </is>
       </c>
-      <c r="E38" t="n">
-        <v>3</v>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>4:5</t>
         </is>
       </c>
     </row>
@@ -2676,12 +4248,24 @@
           <t>Double-goblet alabaster wall sconce shown across seven finish options</t>
         </is>
       </c>
-      <c r="E39" t="n">
-        <v>4</v>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>4:5</t>
         </is>
       </c>
     </row>
@@ -2706,12 +4290,24 @@
           <t>Pair of double-goblet alabaster wall sconces flanking a console table in a living room</t>
         </is>
       </c>
-      <c r="E40" t="n">
-        <v>5</v>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>5:4</t>
         </is>
       </c>
     </row>
@@ -2736,12 +4332,24 @@
           <t>Double-goblet alabaster wall sconce beside a bed with a nightstand plant</t>
         </is>
       </c>
-      <c r="E41" t="n">
-        <v>6</v>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>4:5</t>
         </is>
       </c>
     </row>
@@ -2766,12 +4374,24 @@
           <t>Pair of double-goblet alabaster wall sconces flanking a framed painting in a navy hallway</t>
         </is>
       </c>
-      <c r="E42" t="n">
-        <v>7</v>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>5:4</t>
         </is>
       </c>
     </row>
@@ -2796,12 +4416,24 @@
           <t>Double-goblet alabaster wall sconce beside a bathroom mirror and marble vanity</t>
         </is>
       </c>
-      <c r="E43" t="n">
-        <v>8</v>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>4:3</t>
         </is>
       </c>
     </row>
@@ -2826,12 +4458,24 @@
           <t>Double-goblet alabaster wall sconce glowing warm against a dark wall</t>
         </is>
       </c>
-      <c r="E44" t="n">
-        <v>9</v>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>5:4</t>
         </is>
       </c>
     </row>
@@ -2856,12 +4500,24 @@
           <t>Double-goblet alabaster wall sconce finish options on a grey wall from Antique Patina to Brushed Brass</t>
         </is>
       </c>
-      <c r="E45" t="n">
-        <v>10</v>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>3:2</t>
         </is>
       </c>
     </row>
@@ -2886,12 +4542,24 @@
           <t>Pair of double-goblet alabaster wall sconces flanking a framed landscape painting</t>
         </is>
       </c>
-      <c r="E46" t="n">
-        <v>11</v>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>5:4</t>
         </is>
       </c>
     </row>
@@ -2916,12 +4584,24 @@
           <t>Pair of double-goblet alabaster wall sconces flanking an upholstered bed headboard</t>
         </is>
       </c>
-      <c r="E47" t="n">
-        <v>12</v>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>5:4</t>
         </is>
       </c>
     </row>
@@ -2946,12 +4626,24 @@
           <t>Double-goblet alabaster wall sconce in brushed brass finish on a plain neutral wall</t>
         </is>
       </c>
-      <c r="E48" t="n">
-        <v>13</v>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>4:5</t>
         </is>
       </c>
     </row>
@@ -2976,12 +4668,24 @@
           <t>Double-goblet alabaster wall sconce beside a living room window</t>
         </is>
       </c>
-      <c r="E49" t="n">
-        <v>14</v>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>4:5</t>
         </is>
       </c>
     </row>
@@ -3006,12 +4710,24 @@
           <t>Double-goblet alabaster wall sconce glowing beside a dark bathroom mirror</t>
         </is>
       </c>
-      <c r="E50" t="n">
-        <v>15</v>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>4:5</t>
         </is>
       </c>
     </row>
@@ -3036,12 +4752,24 @@
           <t>Double-goblet alabaster wall sconce glowing warm against a dark charcoal wall</t>
         </is>
       </c>
-      <c r="E51" t="n">
-        <v>16</v>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>4:5</t>
         </is>
       </c>
     </row>
@@ -3066,12 +4794,24 @@
           <t>Pair of double-goblet alabaster wall sconces flanking a console table with laptop and books</t>
         </is>
       </c>
-      <c r="E52" t="n">
-        <v>17</v>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>4:5</t>
         </is>
       </c>
     </row>
@@ -3096,12 +4836,24 @@
           <t>Twin-arm alabaster bell-shade vanity sconce above a console table with a vase and bowl</t>
         </is>
       </c>
-      <c r="E53" t="n">
-        <v>1</v>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>5:4</t>
         </is>
       </c>
     </row>
@@ -3126,12 +4878,24 @@
           <t>Twin-arm alabaster bell-shade wall sconce above a stack of books and a potted fern</t>
         </is>
       </c>
-      <c r="E54" t="n">
-        <v>2</v>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>1:1</t>
         </is>
       </c>
     </row>
@@ -3156,12 +4920,24 @@
           <t>Twin-arm alabaster bell-shade wall sconce glowing against a dark charcoal wall</t>
         </is>
       </c>
-      <c r="E55" t="n">
-        <v>3</v>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>1:1</t>
         </is>
       </c>
     </row>
@@ -3186,12 +4962,24 @@
           <t>Twin-arm alabaster bell-shade wall sconce lighting a dining room table setting</t>
         </is>
       </c>
-      <c r="E56" t="n">
-        <v>4</v>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>1:1</t>
         </is>
       </c>
     </row>
@@ -3216,12 +5004,24 @@
           <t>Twin-arm alabaster bell-shade wall sconce above a console table with dried flower arrangements</t>
         </is>
       </c>
-      <c r="E57" t="n">
-        <v>5</v>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>1:1</t>
         </is>
       </c>
     </row>
@@ -3246,12 +5046,24 @@
           <t>Twin-arm alabaster bell-shade wall sconce in aged brass finish on a plain neutral wall</t>
         </is>
       </c>
-      <c r="E58" t="n">
-        <v>6</v>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>1:1</t>
         </is>
       </c>
     </row>
@@ -3276,12 +5088,24 @@
           <t>Twin-arm alabaster bell-shade wall sconce lighting a hallway console table</t>
         </is>
       </c>
-      <c r="E59" t="n">
-        <v>7</v>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>1:1</t>
         </is>
       </c>
     </row>
@@ -3306,12 +5130,24 @@
           <t>Twin-arm alabaster bell-shade wall sconce above a framed painting in a wood-paneled home office</t>
         </is>
       </c>
-      <c r="E60" t="n">
-        <v>8</v>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>4:5</t>
         </is>
       </c>
     </row>
@@ -3336,12 +5172,24 @@
           <t>Twin-arm alabaster bell-shade wall sconce shown across seven finish options</t>
         </is>
       </c>
-      <c r="E61" t="n">
-        <v>9</v>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>3:2</t>
         </is>
       </c>
     </row>
@@ -3366,12 +5214,24 @@
           <t>Alabaster ball-and-cylinder pillar wall sconce glowing on a dark bedroom wall beside a nightstand</t>
         </is>
       </c>
-      <c r="E62" t="n">
-        <v>1</v>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>3:4</t>
         </is>
       </c>
     </row>
@@ -3396,12 +5256,24 @@
           <t>Alabaster ball-and-cylinder pillar wall sconce above a shelf with a brass owl figurine</t>
         </is>
       </c>
-      <c r="E63" t="n">
-        <v>2</v>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>10:11</t>
         </is>
       </c>
     </row>
@@ -3426,12 +5298,24 @@
           <t>Alabaster ball-and-cylinder pillar wall sconces lighting a hallway at night</t>
         </is>
       </c>
-      <c r="E64" t="n">
-        <v>3</v>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>3:4</t>
         </is>
       </c>
     </row>
@@ -3456,12 +5340,24 @@
           <t>Pair of alabaster ball-and-cylinder pillar wall sconces flanking a bed headboard</t>
         </is>
       </c>
-      <c r="E65" t="n">
-        <v>4</v>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>3:4</t>
         </is>
       </c>
     </row>
@@ -3486,12 +5382,24 @@
           <t>Alabaster ball-and-cylinder pillar wall sconce in aged brass finish on a plain neutral wall</t>
         </is>
       </c>
-      <c r="E66" t="n">
-        <v>5</v>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>3:4</t>
         </is>
       </c>
     </row>
@@ -3516,12 +5424,24 @@
           <t>Close-up of alabaster ball-and-cylinder pillar wall sconce on a linen-textured wall</t>
         </is>
       </c>
-      <c r="E67" t="n">
-        <v>6</v>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>3:4</t>
         </is>
       </c>
     </row>
@@ -3546,12 +5466,24 @@
           <t>Alabaster ball-and-cylinder pillar wall sconce beside an armchair and side table</t>
         </is>
       </c>
-      <c r="E68" t="n">
-        <v>7</v>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>3:4</t>
         </is>
       </c>
     </row>
@@ -3576,12 +5508,24 @@
           <t>Alabaster ball-and-cylinder pillar wall sconce shown across seven finish options</t>
         </is>
       </c>
-      <c r="E69" t="n">
-        <v>8</v>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>3:2</t>
         </is>
       </c>
     </row>
@@ -3606,12 +5550,24 @@
           <t>Pair of alabaster ball-and-cylinder pillar wall sconces flanking framed artwork in a home office</t>
         </is>
       </c>
-      <c r="E70" t="n">
-        <v>9</v>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>5:4</t>
         </is>
       </c>
     </row>
@@ -3636,12 +5592,24 @@
           <t>Ball-finial alabaster cone-shade wall sconce beside a bathroom mirror and marble vanity</t>
         </is>
       </c>
-      <c r="E71" t="n">
-        <v>1</v>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>2:3</t>
         </is>
       </c>
     </row>
@@ -3666,12 +5634,24 @@
           <t>Ball-finial alabaster cone-shade wall sconce beside a bed with a laptop and notebook on the nightstand</t>
         </is>
       </c>
-      <c r="E72" t="n">
-        <v>2</v>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>2:3</t>
         </is>
       </c>
     </row>
@@ -3696,12 +5676,24 @@
           <t>Ball-finial alabaster cone-shade wall sconce glowing on a dark wall beside a brass antelope figurine</t>
         </is>
       </c>
-      <c r="E73" t="n">
-        <v>3</v>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>1:1</t>
         </is>
       </c>
     </row>
@@ -3726,12 +5718,24 @@
           <t>Pair of ball-finial alabaster cone-shade wall sconces flanking framed art in a wood-paneled office</t>
         </is>
       </c>
-      <c r="E74" t="n">
-        <v>4</v>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>2:3</t>
         </is>
       </c>
     </row>
@@ -3756,12 +5760,24 @@
           <t>Ball-finial alabaster cone-shade wall sconce in brushed brass finish on a plain neutral wall</t>
         </is>
       </c>
-      <c r="E75" t="n">
-        <v>5</v>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2:3</t>
         </is>
       </c>
     </row>
@@ -3786,12 +5802,24 @@
           <t>Ball-finial alabaster cone-shade wall sconce above a console table with a laptop</t>
         </is>
       </c>
-      <c r="E76" t="n">
-        <v>6</v>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>2:3</t>
         </is>
       </c>
     </row>
@@ -3816,12 +5844,24 @@
           <t>Ball-finial alabaster cone-shade wall sconce shown across seven finish options</t>
         </is>
       </c>
-      <c r="E77" t="n">
-        <v>7</v>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>3:2</t>
         </is>
       </c>
     </row>
@@ -3846,12 +5886,24 @@
           <t>Ball-finial alabaster cone-shade wall sconce beside a curtained window and a vase of greenery</t>
         </is>
       </c>
-      <c r="E78" t="n">
-        <v>8</v>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>4:5</t>
         </is>
       </c>
     </row>
@@ -3876,12 +5928,24 @@
           <t>Pair of bell-jar alabaster wall sconces flanking a round mirror above a subway-tile bathroom vanity</t>
         </is>
       </c>
-      <c r="E79" t="n">
-        <v>1</v>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>2:3</t>
         </is>
       </c>
     </row>
@@ -3906,12 +5970,24 @@
           <t>Bell-jar alabaster wall sconce glowing beside a leather armchair and stone fireplace</t>
         </is>
       </c>
-      <c r="E80" t="n">
-        <v>2</v>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>2:3</t>
         </is>
       </c>
     </row>
@@ -3936,12 +6012,24 @@
           <t>Pair of bell-jar alabaster wall sconces flanking a gilt mirror in a wood-paneled hallway</t>
         </is>
       </c>
-      <c r="E81" t="n">
-        <v>3</v>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>2:3</t>
         </is>
       </c>
     </row>
@@ -3966,12 +6054,24 @@
           <t>Bell-jar alabaster wall sconces lighting a curved staircase gallery wall</t>
         </is>
       </c>
-      <c r="E82" t="n">
-        <v>4</v>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>2:3</t>
         </is>
       </c>
     </row>
@@ -3996,12 +6096,24 @@
           <t>Bell-jar alabaster wall sconce lighting an exterior cottage doorway with wisteria</t>
         </is>
       </c>
-      <c r="E83" t="n">
-        <v>5</v>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>2:3</t>
         </is>
       </c>
     </row>
@@ -4026,12 +6138,24 @@
           <t>Bell-jar alabaster wall sconce beside a round mirror above a wooden desk with a laptop</t>
         </is>
       </c>
-      <c r="E84" t="n">
-        <v>6</v>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>4:5</t>
         </is>
       </c>
     </row>
@@ -4056,12 +6180,24 @@
           <t>Bell-jar alabaster wall sconce above a console table with a phone and tablet</t>
         </is>
       </c>
-      <c r="E85" t="n">
-        <v>7</v>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>4:5</t>
         </is>
       </c>
     </row>
@@ -4086,12 +6222,24 @@
           <t>Bell-jar alabaster wall sconce glowing on a dark wall beside a carved stone sculpture</t>
         </is>
       </c>
-      <c r="E86" t="n">
-        <v>8</v>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>1:1</t>
         </is>
       </c>
     </row>
@@ -4116,12 +6264,24 @@
           <t>Bell-jar alabaster wall sconce shown across seven finish options</t>
         </is>
       </c>
-      <c r="E87" t="n">
-        <v>9</v>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>2:3</t>
         </is>
       </c>
     </row>
@@ -4146,12 +6306,24 @@
           <t>Row of bell-jar alabaster wall sconces lighting a hallway at night</t>
         </is>
       </c>
-      <c r="E88" t="n">
-        <v>10</v>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>4:5</t>
         </is>
       </c>
     </row>
@@ -4176,12 +6348,24 @@
           <t>Bell-jar alabaster wall sconce in aged brass finish, glowing warm against a plain dark wall</t>
         </is>
       </c>
-      <c r="E89" t="n">
-        <v>11</v>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>2:3</t>
         </is>
       </c>
     </row>
@@ -4206,21 +6390,3310 @@
           <t>Bell-jar alabaster wall sconce beside an armchair and side table with books</t>
         </is>
       </c>
-      <c r="E90" t="n">
-        <v>12</v>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>4:5</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>ALK-001</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/19cgTvKdD_oM2y7HyBh6srmANlItqYl-G/view</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Hero</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>ArtLoka alabaster cone-shade wall sconce close-up, lit, with a softly blurred bathroom and tub in the background</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>ALK-001</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/12FVxdFNj92YAMmAwYQboUIqUQOMz2EhA/view</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Alabaster cone-shade wall sconce beside a front door in a daylight entryway, next to a round mirror and console table</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>2:3</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>ALK-001</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1pX7aUdGctTQICdqLLANqngaf-z8czaBT/view</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Alabaster cone-shade wall sconce lighting a dark wood-paneled hallway with a console table and mirror</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>3:2</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>ALK-001</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1K2fIav8DXw-zcAT1S2JOPju0k6K7SfmN/view</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Comparison</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Alabaster cone-shade wall sconce shown across seven finish options: Antique Patina, Raw Brass, Blackened Brass, Antique Black, Polished Chrome, Polished Brass, Brushed Brass</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>4:3</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>ALK-001</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/132m8LOX3_sMzj8tSQpzN6HGuLFdUb9Yp/view</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Alabaster cone-shade wall sconce above a wooden nightstand with a potted fern, book, and mug</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>ALK-001</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/139VtoWMkdFwimFAmi1JzTi2OIE0lOOty/view</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Pair of alabaster cone-shade wall sconces flanking a bed headboard, glowing warm at night</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>ALK-001</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1jBsw8OH-7NRGNNnfwzfYwk0JjzDSKUQZ/view</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Alabaster cone-shade wall sconce lit above a rustic wood bed and nightstand with a potted plant</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>4:3</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>ALK-001</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1mKNoLdP60nL0RK02apc48LDgME1upytw/view</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Close-up of alabaster cone-shade wall sconce showing natural stone veining and brass ball-joint arm, dark bedroom background</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>4:3</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>ALK-001</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1NH7qeYgC4SFNZ4JO9zZKPy15s5o5gAye/view</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Close-up side view of alabaster cone-shade wall sconce on a plain putty-grey wall</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>4:5</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>ALK-001</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1Gsc8OvRqoDXjKKeAyueFPUTvwAmtOuIp/view</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Alabaster cone-shade wall sconce above a rustic wood headboard with nightstand, plant, and books, daylight</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>ALK-001</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/18kAtyqWsuEWIVf4UgijzOmwQPcFWnukQ/view</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Alabaster cone-shade wall sconce above a rustic wood bed with nightstand, plant, and books</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>4:3</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>ALK-001</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1H0vMkvGXpTcYI1TGQ4LfhSWqhfHkqzs2/view</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Alabaster cone-shade wall sconce beside a console table with a vase of greenery in a hallway</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>3:4</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>ALK-001</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1Wvv6IGGeALD9mZoF9FuEkHCecIONH3NB/view</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Alabaster cone-shade wall sconce in a hallway beside a dark wood door and framed landscape painting</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>ALK-030</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1w0c5bCtw3WwtT-CtNUdjKcblLFqd0YU8/view</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Hero</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>ArtLoka brass gooseneck wall sconce with scalloped glass shade, lit, on a dark navy wall beside a brass owl figurine</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>2:3</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>ALK-030</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1dJb4F2lFIpNkNpCDfbYsZ3Hv-zsWZ93u/view</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Pair of brass gooseneck wall sconces flanking an ornate mirror above a dark-tile bathroom vanity with orchids</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>ALK-030</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1Z9q8PNYqNvtO5UesJtGY8-2e_VrVD-7n/view</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Brass gooseneck wall sconce lighting a cozy reading nook with a leather armchair, coffee, and books</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>ALK-030</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1Wf_ga4-0q4EejOG6fWxxMSeZMmVRyXRP/view</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Brass gooseneck wall sconce on an exposed brick wall in a living room with sofa, coat rack, and plant</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>ALK-030</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/152Hzc2CkXbquFuUS9sHvSj_1b2UpTtwz/view</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Brass gooseneck wall sconces lighting a staircase hallway lined with framed family photos</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>ALK-030</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1rv_Cgdz1_bFiWIPX0kQWU4QU-zqM4g3-/view</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Brass gooseneck wall sconce on a log cabin porch beside a wooden door, rocking chair, and snowy view</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>ALK-030</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1iUd2FuF1A5VzxOiPxXm8hxIzOVdLM0HG/view</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Brass gooseneck wall sconce above a dark wood nightstand with a laptop, phone, and book</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>2:3</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>ALK-030</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1hxpn1DhzRii0Qgi-wzqa5bWTyJ9r9hPg/view</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Brass gooseneck wall sconce lighting a dark hallway corridor with framed art and a console table</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>2:3</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>ALK-030</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1nLTyBJxZ92VDjoYrWv0XL1zfDBWxC5dY/view</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Comparison</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Brass gooseneck wall sconce with scalloped glass shade shown across seven finish options: Antique Patina, Raw Brass, Blackened Brass, Antique Black, Polished Chrome, Polished Brass, Brushed Brass</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>ALK-030</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1lygOp8Af3V3GiCcMrx5QwiMjPhVMqpI0/view</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Brass gooseneck wall sconces lighting a staircase with wooden handrail and a side table</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>2:3</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>ALK-030</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1MC0hmX0dzT2FbsESZeri7Zsq65V_cM-2/view</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Close-up of brass gooseneck wall sconce with scalloped glass shade on a plain cream-grey wall</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>ALK-030</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1NIYcvo2JgHmBReCXb9GZmsgoegCKr6SD/view</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Close-up of brass gooseneck wall sconce lit in a dark wood-paneled reading room beside a leather armchair</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>2:3</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>ALK-030</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1PB8V4_a2WyE2OC2-TGNq5MnPyIalAVqA/view</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Brass gooseneck wall sconce in a dark wood-paneled reading room with leather armchair, throw, and snowy window</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>5:4</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>ALK-030</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1aqJOIf0P9ZjmA0uPvdzbvWc1we_3hpH0/view</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Pair of brass gooseneck wall sconces flanking an ornate gold mirror above a dark-tile bathroom vanity</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>5:4</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>ALK-030</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/15S00fANwvpOAw90q6JsekYLXiWGgJ4AH/view</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Brass gooseneck wall sconce on an exposed brick wall beside a mirror, potted plant, and coat rack</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>5:4</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>ALK-031</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/17_3ExgdkEsJ47RobAx5-IYXoTTGFqTdV/view</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Hero</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>ArtLoka solid brass alabaster cylinder sconce, lit, on a dark navy wall beside a brass owl figurine</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>ALK-031</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1oad8LWP-LubCZQAx3fDKCyKY62GfYFsS/view</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Solid brass alabaster cylinder sconce above a wooden nightstand with laptop, tablet, and phone</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>ALK-031</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1QhCuBrxc8pvsnbf-jtxkbGoAtOcn4HRD/view</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Comparison</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Solid brass alabaster cylinder sconce shown across seven finish options: Antique Patina, Raw Brass, Blackened Brass, Antique Black, Polished Chrome, Polished Brass, Brushed Brass</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>ALK-031</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1vIy8yQi8Z09nsJGLqlYCCMYGSr85Ldfl/view</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Pair of solid brass alabaster cylinder sconces flanking an upholstered bed headboard</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>ALK-031</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1Cm24hgtOhLX_Pjaj3KIkjEmjwl7HiWGD/view</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Close-up of solid brass alabaster cylinder sconce with ball-drop rod on a plain putty-grey wall</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>ALK-031</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1CuBRJXTXTRQKjJuL3vEdxFkyy8tLHV-0/view</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Solid brass alabaster cylinder sconce above a dark wood desk with laptop and phone</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>ALK-031</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1CNAoNBrfvNsNmuhDdZkP2_7MA59T4ocu/view</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Solid brass alabaster cylinder sconce beside a leather armchair and fireplace in a log cabin living room</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>ALK-031</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1GptKkHGjBms5GNfviFQiHkby2gAbhTPp/view</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Solid brass alabaster cylinder sconce above a hotel-style desk and shelving with a city skyline view</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>6:5</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>ALK-031</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1tQrmKQ6vAX0AOyYet8pVT2GfQnumGGWE/view</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Pair of solid brass alabaster cylinder sconces flanking a mirror above a dark green-tile bathroom vanity</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>5:4</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>ALK-031</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1c---QA6PySETmIH8uJKTnsA-khXTJrNw/view</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Solid brass alabaster cylinder sconce lighting a wood-paneled staircase hallway lined with portraits</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>5:4</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>ALK-021</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1_QMNhUhCvY3pua2ze5MYoeZERqL22UEo/view</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Hero</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>ArtLoka alabaster moon-disc wall sconce glowing warm on a dark navy wall beside brass elephant figurines</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>ALK-021</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1y8Fb13rg6_nKS6Nx9GEXlv_D1bjZVMcU/view</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Alabaster moon-disc wall sconce beside an olive plant and armchair, above a coffee table with laptop and mug</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>4:5</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>ALK-021</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1ZzRIH3gANhcz1_2eK1Ezp9h6f9yo3uKg/view</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Alabaster moon-disc wall sconce glowing on a dark staircase hallway wall</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>4:5</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>ALK-021</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1C6JoIySVpShYPUbZaI9VktBbnBQf6tGE/view</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Pair of alabaster moon-disc wall sconces glowing above a console table with laptop, mug, and books</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>4:5</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>ALK-021</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1Rzawmj2z0bB9SQk5JnxMeiPICC7Js6hO/view</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Alabaster moon-disc wall sconce glowing beside a bathroom mirror above a dark marble vanity</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>4:5</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>ALK-021</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1TQgjxz4xaZGkfGIZLCRljQ3iWsR2sbGk/view</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Close-up of alabaster moon-disc wall sconce showing natural stone veining and brass center knob, plain grey background</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>4:5</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>ALK-021</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1rt5ONMT5g-EzYnBtTBkc7tfjErzKpV6l/view</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Comparison</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Alabaster moon-disc wall sconce shown across six available disc sizes, side by side</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>ALK-002</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1QtEoIbCw29HNbBncD_bG0UUgfWm-a4eS/view</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Pair of ruffled tulip-bell alabaster wall sconces flanking a framed architectural print in a dark wood-paneled study</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>3:4</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>ALK-002</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1trmEA5Ng_JnRS6uk2_3Y2CrE4GZM1HfH/view</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Ruffled tulip-bell alabaster wall sconce lit beside a bookshelf, velvet armchair, and antique book</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>3:4</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>ALK-002</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1nhLkjOgTmSdeBYT84d5-z_NEj70M2B2I/view</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Close-up of ruffled tulip-bell alabaster wall sconce on a plain putty-grey wall</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>3:4</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>ALK-002</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1YMDUAOs_RyLqwNkFaKmFhC479QVDvQPk/view</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Ruffled tulip-bell alabaster wall sconce above a nightstand with laptop and phone, sofa visible beyond</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>3:4</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>ALK-002</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1Krvbg4bVOdjyF3NVfGSNamhfUFCVF9hg/view</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Ruffled tulip-bell alabaster wall sconce above a console table with laptop, books, and phone</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>3:4</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>ALK-002</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/196c44J-n7EBRwBjaaPStONXCZM-zfQfv/view</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Ruffled tulip-bell alabaster wall sconce beside a rustic stone cottage doorway with wellies and a door mat</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>3:4</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>ALK-002</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1NjsBKBtvhEQZyXJ-nWV6rS-gc9yTlCBW/view</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Ruffled tulip-bell alabaster wall sconce above a wooden side table beside an upholstered armchair</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>3:4</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>ALK-002</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/142SKaEyh74F1evW0TVM2emOB9gAIgc19/view</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Pair of ruffled tulip-bell alabaster wall sconces flanking a mirror above a rustic stone bathroom vanity</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>3:4</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>ALK-002</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1s-Ql0TC6JiNzWSSYll2KB9qLezaoLnT7/view</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Three ruffled tulip-bell alabaster wall sconces above a fireplace mantle with framed maps</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>3:4</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>ALK-002</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/12ctZQpu1ACxbCHJXmR6B0NC2bq75tNh5/view</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Comparison</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Ruffled tulip-bell alabaster wall sconce shown across seven finish options: Antique Patina, Raw Brass, Blackened Brass, Antique Black, Polished Chrome, Polished Brass, Brushed Brass</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>3:4</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>ALK-002</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1oybxqiSxAMnZr46dL2F38qPVPXZ7g_HW/view</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Hero</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>ArtLoka ruffled tulip-bell alabaster wall sconce glowing warm on a dark wall beside a bonsai tree</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>ALK-002</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1d6PrEMez03TmDHlpLg0jZrInT_XS5Sz1/view</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Ruffled tulip-bell alabaster wall sconce above a study desk with a globe, compass, and stacked books</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>3:4</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>ALK-003</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1QjhvEgr-8AaOeB5EUentu5A4vBjFCxYu/view</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Hero</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Modern alabaster and brass bedside wall sconce lit against a dark charcoal wall, showing stacked alabaster orbs and a conical brass shade (ArtLoka ALK-003)</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>ALK-003</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/11y_rwFTTteMSQrT_pCXpfd5VD3E6l1hv/view</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Alabaster and brass wall sconce glowing above a wood nightstand with a laptop, beside a bed (ArtLoka ALK-003)</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>4:5</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>ALK-003</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1jkJA7FGaSGXC4ccgNHvr5g0YTtf1F02c/view</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Alabaster and brass wall sconce beside a black-framed mirror over a marble bathroom vanity (ArtLoka ALK-003)</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>4:5</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>ALK-003</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1SP_ih5juaNKznKFfU5YJ1_yntu8uCmsf/view</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Pair of alabaster and brass wall sconces flanking mirrors above a marble bathroom vanity (ArtLoka ALK-003)</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>4:5</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>ALK-003</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1tOMFcAm3xRiBB6KytxSsC4zwtzCc4NHv/view</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Alabaster and brass wall sconce in a bright entryway beside a window and wood console table (ArtLoka ALK-003)</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>4:5</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>ALK-003</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1xV7VKlvz6XZGoGObs2nW_3XTMrTsZSbt/view</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Close-up of the alabaster and brass bedside sconce on a neutral background, showing stacked alabaster orbs and conical brass shade (ArtLoka ALK-003)</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>ALK-003</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1gijJeiFEQLNpHIZWxyWmi6-2xs1Szvtr/view</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Comparison</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Alabaster and brass wall sconce shown in eight finishes: raw brass, polished brass, antique patina, blackened brass, brushed chrome, polished chrome, brushed brass, black matte (ArtLoka ALK-003)</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>ALK-003</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1YBPS0bUPxAHaAvCOYFeG2sKGj7YqwxsZ/view</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Pair of alabaster and brass wall sconces flanking an upholstered headboard in a dark bedroom at night (ArtLoka ALK-003)</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>ALK-004</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1CwVFKbB6cFVgepcGL96kqV3ZDyu3NmCV/view</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Alabaster double wall sconce with bell-shaped shades and black-and-white sphere accents beside a bathroom mirror over a marble vanity (ArtLoka ALK-004)</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>2:3</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>ALK-004</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1UiVJK40uc4DEhhx6k90720n3yjSPCrWf/view</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Hero</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Alabaster double wall sconce in antique brass with two bell-shaped shades and sphere accents, on a dark background (ArtLoka ALK-004)</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>2:3</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>ALK-004</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1nIb_4ABSDsviusrEj9jz99Fe15QPbgpI/view</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Alabaster double wall sconce glowing above a wood nightstand beside a bed (ArtLoka ALK-004)</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>ALK-004</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1MkgaMFkbS2mOgxX2iNxRvgqk4Pz8zrpG/view</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Comparison</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Alabaster double wall sconce shown in seven finishes: raw brass, antique patina, brushed brass, polished brass, brushed chrome, polished chrome, black matte (ArtLoka ALK-004)</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>ALK-004</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1HKEXOJKU2_rbSi5taAQ8P7P0ApLK9Er9/view</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Alabaster double wall sconce on a pale wall above a console table in a bright entryway (ArtLoka ALK-004)</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>ALK-004</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/17SXhIE_OnMxzpAAA0nWkqNM1jnKMsaoN/view</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Alabaster double wall sconce casting a warm glow above a side table in a living room at dusk (ArtLoka ALK-004)</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>ALK-004</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1nR7Ua1cv3HmefksZGu7MYzI2nfZcuw6v/view</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Close-up of the alabaster double wall sconce on a neutral background, showing the bell-shaped shades and sphere accents (ArtLoka ALK-004)</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>ALK-005</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1m4Cto-1DgIllzD3ctodYCLCyQaJOdzn6/view</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Handmade brass double sconce with cylindrical alabaster shades beside a bathroom mirror over a dark vanity (ArtLoka ALK-005)</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>2:3</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>ALK-005</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1A4mYOGer2sc_vFH93JT5fpEsj9DgLGbb/view</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Handmade brass double sconce with cylindrical alabaster shades above a nightstand beside an upholstered bed (ArtLoka ALK-005)</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>3:2</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>ALK-005</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1x4zSbsLg2yfxPGHktCOIOvtRFda8ce_V/view</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Handmade brass double sconce glowing above a wood nightstand beside a bed (ArtLoka ALK-005)</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>3:2</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>ALK-005</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1PyoR-Xuy1N5buSUgCP2sZOOu0Ukm_sdf/view</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Handmade brass double sconce lighting a mirror above a wood vanity with a round vessel sink (ArtLoka ALK-005)</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>3:2</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>ALK-005</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1MQUA1_qtVJ3lhe4hFQOQqpWJmVusYqFB/view</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Handmade brass double sconce beside framed artwork above a hallway console table (ArtLoka ALK-005)</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>2:3</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>ALK-005</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1ItVTFQzB-JVSdI11V_MrgmO9FaCboOUn/view</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Hero</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Handmade brass double sconce with cylindrical alabaster shades shown horizontally on a dark background (ArtLoka ALK-005)</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>3:4</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>ALK-005</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1KmKI7oxkE7SP0SUIHfXhXxui55yID2UU/view</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Comparison</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Handmade brass double sconce shown in seven finishes: raw brass, brushed brass, antique patina, polished brass, brushed chrome, polished chrome, black matte (ArtLoka ALK-005)</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>4:5</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>ALK-005</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1ktGk1UYE-uqK3wfdXi3TA-b3VTeEvtdc/view</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Handmade brass double sconce shown vertically on a dark background, showing two cylindrical alabaster shades and brass sphere accents (ArtLoka ALK-005)</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>4:5</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>ALK-005</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1jVZlTH991dK-dPKa9051UJp1mB6Nhjxd/view</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Handmade brass double sconce in a warm-lit hallway beside framed art and a console table (ArtLoka ALK-005)</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>2:3</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="F2:F90" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>